--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_AnhTuanNB(NamAnh)_150826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_AnhTuanNB(NamAnh)_150826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2579DD68-7E0D-4B07-A5AF-D85C67B89AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3A539A-3831-40E1-9156-D151E962C7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -128,7 +128,7 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Đang chờ phản hồi lại báo giá từ KD. Lực</t>
+    <t>Khách đã đồng ý báo giá sửa chữa, công nợ ghi KD. Lực</t>
   </si>
 </sst>
 </file>
@@ -498,6 +498,78 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -515,78 +587,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,26 +1025,26 @@
       <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="59"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="15"/>
@@ -1055,11 +1055,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1069,11 +1069,11 @@
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="27" t="s">
@@ -1086,11 +1086,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
@@ -1206,21 +1206,23 @@
         <f>SUM(H12*I12)</f>
         <v>130000</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="31" t="s">
+        <v>34</v>
+      </c>
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="59"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="22">
         <f>SUM(J11:J12)</f>
         <v>260000</v>
@@ -1255,37 +1257,37 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="60" t="s">
+      <c r="G16" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
@@ -1343,20 +1345,20 @@
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" s="62" t="s">
+      <c r="A22" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
       <c r="K22" s="11"/>
       <c r="AA22" s="2"/>
     </row>
@@ -1434,6 +1436,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="G17:J17"/>
@@ -1441,16 +1453,6 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
